--- a/AI-Excel-Agent/AI_Talks_Sales_Workbook.xlsx
+++ b/AI-Excel-Agent/AI_Talks_Sales_Workbook.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SalesData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ReadMe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AIReport" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SalesData'!$A$1:$J$61</definedName>
@@ -80,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -107,6 +108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3483,4 +3485,90 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>AI Excel Agent — Sales Analysis Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Generated summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>The analysis identified the three lowest-revenue products: Wireless Mouse (revenue $407.75), Webcam HD (revenue $933.75), and Mechanical Keyboard (revenue $1,719.50). Regional sales show that the North region leads with $22,401.50 in revenue (35.95% share) and 62 units sold, followed by the South region with $19,328.50 (31.02%). The West and East regions each contribute roughly 16.5% of total revenue, with lower unit counts. These insights highlight product and regional performance disparities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Consider targeted promotions or bundles for the lowest-revenue products (Wireless Mouse, Webcam HD, Mechanical Keyboard) to boost their sales volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Allocate additional marketing resources to the high-performing North and South regions while exploring growth opportunities in the West and East regions through localized campaigns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Review inventory levels for low-revenue items to avoid overstock and align supply with demand, possibly using them as add‑ons in orders from high-revenue regions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>